--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -7752,7 +7752,7 @@
         <v>117965024</v>
       </c>
       <c r="B60" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8096,7 +8096,7 @@
         <v>119907574</v>
       </c>
       <c r="B63" t="n">
-        <v>57937</v>
+        <v>57947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8096,7 +8096,7 @@
         <v>119907574</v>
       </c>
       <c r="B63" t="n">
-        <v>57947</v>
+        <v>57985</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8096,11 +8096,11 @@
         <v>119907574</v>
       </c>
       <c r="B63" t="n">
-        <v>58003</v>
+        <v>58008</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8110,11 +8110,6 @@
       </c>
       <c r="E63" t="n">
         <v>102125</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8096,7 +8096,7 @@
         <v>119907574</v>
       </c>
       <c r="B63" t="n">
-        <v>58008</v>
+        <v>58012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8110,6 +8110,11 @@
       </c>
       <c r="E63" t="n">
         <v>102125</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8096,7 +8096,7 @@
         <v>119907574</v>
       </c>
       <c r="B63" t="n">
-        <v>58012</v>
+        <v>58013</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6572,10 +6572,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116443678</v>
+        <v>116659658</v>
       </c>
       <c r="B50" t="n">
-        <v>56924</v>
+        <v>56925</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6607,27 +6607,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sågviken Laxforsen, T lm</t>
+          <t>Sågviken, Laxforsen, T lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>731550</v>
+        <v>731467</v>
       </c>
       <c r="R50" t="n">
-        <v>7537353</v>
+        <v>7537292</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6674,22 +6674,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Åke Flygare</t>
+          <t>Ylva Sarri</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Åke Flygare</t>
+          <t>Ylva Sarri</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116654787</v>
+        <v>116654788</v>
       </c>
       <c r="B51" t="n">
-        <v>56925</v>
+        <v>56931</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6698,25 +6698,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102964</v>
+        <v>102966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6724,11 +6724,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6810,10 +6814,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116659658</v>
+        <v>116659483</v>
       </c>
       <c r="B52" t="n">
-        <v>56925</v>
+        <v>56336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6822,25 +6826,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6852,7 +6856,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6924,10 +6928,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116654788</v>
+        <v>116781943</v>
       </c>
       <c r="B53" t="n">
-        <v>56931</v>
+        <v>56977</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6936,25 +6940,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102966</v>
+        <v>100063</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6962,28 +6966,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sågviken, Laxforsen, T lm</t>
+          <t>Lintasenniva (Lintasenniva), T lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>731492</v>
+        <v>731628</v>
       </c>
       <c r="R53" t="n">
-        <v>7537275</v>
+        <v>7537101</v>
       </c>
       <c r="S53" t="n">
         <v>200</v>
@@ -7010,22 +7002,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7040,22 +7032,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marit Sikku Trägårdh</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marit Sikku Trägårdh, Lotta Nygård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116659483</v>
+        <v>116859499</v>
       </c>
       <c r="B54" t="n">
-        <v>56336</v>
+        <v>56977</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7064,53 +7056,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100045</v>
+        <v>100063</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>rastande</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sågviken, Laxforsen, T lm</t>
+          <t>Lintasenniva (Lintasenniva), T lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>731467</v>
+        <v>731605</v>
       </c>
       <c r="R54" t="n">
-        <v>7537292</v>
+        <v>7537311</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7134,12 +7123,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7154,22 +7153,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ylva Sarri</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ylva Sarri</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116738170</v>
+        <v>117965024</v>
       </c>
       <c r="B55" t="n">
-        <v>56931</v>
+        <v>56754</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7178,57 +7177,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102966</v>
+        <v>102961</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sågviken, Laxforsen, T lm</t>
+          <t>laxforsen (laxforsen), T lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>731604</v>
+        <v>731621</v>
       </c>
       <c r="R55" t="n">
-        <v>7537186</v>
+        <v>7537084</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7252,12 +7235,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7272,22 +7265,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116738327</v>
+        <v>119159510</v>
       </c>
       <c r="B56" t="n">
-        <v>56925</v>
+        <v>57951</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7296,53 +7289,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102964</v>
+        <v>103042</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sågviken, Laxforsen, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>731604</v>
+        <v>731289</v>
       </c>
       <c r="R56" t="n">
-        <v>7537186</v>
+        <v>7537034</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7366,12 +7355,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7386,22 +7385,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>Anders Eriksson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>Anders Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116781943</v>
+        <v>119165574</v>
       </c>
       <c r="B57" t="n">
-        <v>56977</v>
+        <v>96860</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7410,45 +7409,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100063</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lintasenniva (Lintasenniva), T lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>731628</v>
+        <v>731364</v>
       </c>
       <c r="R57" t="n">
-        <v>7537101</v>
+        <v>7537111</v>
       </c>
       <c r="S57" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7472,22 +7467,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7502,74 +7497,73 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116859499</v>
+        <v>119907574</v>
       </c>
       <c r="B58" t="n">
-        <v>56977</v>
+        <v>58107</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100063</v>
+        <v>102125</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lintasenniva (Lintasenniva), T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>731605</v>
+        <v>730908</v>
       </c>
       <c r="R58" t="n">
-        <v>7537311</v>
+        <v>7536824</v>
       </c>
       <c r="S58" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7593,22 +7587,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7623,22 +7617,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Aron Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Aron Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117031040</v>
+        <v>123933346</v>
       </c>
       <c r="B59" t="n">
-        <v>56980</v>
+        <v>56541</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7647,53 +7641,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100063</v>
+        <v>100045</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sågviken, Laxforsen, T lm</t>
+          <t>Lintasenniva, Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>731604</v>
+        <v>731563</v>
       </c>
       <c r="R59" t="n">
-        <v>7537186</v>
+        <v>7537397</v>
       </c>
       <c r="S59" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7717,12 +7708,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7737,479 +7738,15 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Barbro Hermansson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>117965024</v>
-      </c>
-      <c r="B60" t="n">
-        <v>56754</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>102961</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Drillsnäppa</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Actitis hypoleucos</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>laxforsen (laxforsen), T lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>731621</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7537084</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>119159510</v>
-      </c>
-      <c r="B61" t="n">
-        <v>57951</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>103042</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Grönfink</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Chloris chloris</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Luossalahti, T lm</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>731289</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7537034</v>
-      </c>
-      <c r="S61" t="n">
-        <v>50</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Anders Eriksson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Anders Eriksson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>119165574</v>
-      </c>
-      <c r="B62" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lintasenniva (Lintasenniva), T lm</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>731364</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7537111</v>
-      </c>
-      <c r="S62" t="n">
-        <v>5</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Jacob Björnberg</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Jacob Björnberg</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>119907574</v>
-      </c>
-      <c r="B63" t="n">
-        <v>58107</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>102125</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Pinicola enucleator</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Luossalahti, T lm</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>730908</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7536824</v>
-      </c>
-      <c r="S63" t="n">
-        <v>4</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Aron Andersson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Aron Andersson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7748,6 +7748,122 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124001743</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56541</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>731621</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7537096</v>
+      </c>
+      <c r="S60" t="n">
+        <v>200</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7864,6 +7864,108 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124095958</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56541</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>731475</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7537386</v>
+      </c>
+      <c r="S61" t="n">
+        <v>200</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7966,6 +7966,120 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124130175</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56541</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>731604</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7537186</v>
+      </c>
+      <c r="S62" t="n">
+        <v>100</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8428,6 +8428,569 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124724006</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57143</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>731578</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7537099</v>
+      </c>
+      <c r="S66" t="n">
+        <v>90</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124712615</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56620</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100006</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Stjärtand</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>731442</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7537393</v>
+      </c>
+      <c r="S67" t="n">
+        <v>200</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>124722787</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56689</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100079</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Salskrake</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mergellus albellus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>731461</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7537423</v>
+      </c>
+      <c r="S68" t="n">
+        <v>200</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124723379</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>731461</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7537423</v>
+      </c>
+      <c r="S69" t="n">
+        <v>200</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>124722855</v>
+      </c>
+      <c r="B70" t="n">
+        <v>56620</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100006</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stjärtand</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>731461</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7537423</v>
+      </c>
+      <c r="S70" t="n">
+        <v>200</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B64" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,28 +8214,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8314,10 +8318,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B65" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8326,32 +8330,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8991,6 +8991,238 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>124780623</v>
+      </c>
+      <c r="B71" t="n">
+        <v>56620</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100006</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stjärtand</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>731604</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7537186</v>
+      </c>
+      <c r="S71" t="n">
+        <v>100</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124780549</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57143</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>731604</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7537186</v>
+      </c>
+      <c r="S72" t="n">
+        <v>100</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Barbro Hermansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124724006</v>
+        <v>124722855</v>
       </c>
       <c r="B66" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,41 +8442,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R66" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S66" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8505,7 +8514,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8515,7 +8524,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8542,10 +8551,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124712615</v>
+        <v>124724006</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,41 +8563,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731442</v>
+        <v>731578</v>
       </c>
       <c r="R67" t="n">
-        <v>7537393</v>
+        <v>7537099</v>
       </c>
       <c r="S67" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8615,9 +8624,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,22 +8651,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124722787</v>
+        <v>124712615</v>
       </c>
       <c r="B68" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8656,42 +8675,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R68" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S68" t="n">
         <v>200</v>
@@ -8721,19 +8736,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>20:51</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>20:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8748,12 +8753,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8865,17 +8870,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722855</v>
+        <v>124722787</v>
       </c>
       <c r="B70" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8884,35 +8889,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B64" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,32 +8214,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8318,10 +8314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B65" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8330,28 +8326,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8430,7 +8430,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124722855</v>
+        <v>124712615</v>
       </c>
       <c r="B66" t="n">
         <v>56620</v>
@@ -8463,26 +8463,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R66" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S66" t="n">
         <v>200</v>
@@ -8512,19 +8503,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>20:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8539,22 +8520,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124724006</v>
+        <v>124723379</v>
       </c>
       <c r="B67" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8563,20 +8544,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8587,17 +8568,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R67" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S67" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8626,7 +8607,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8636,7 +8617,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8663,10 +8644,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124712615</v>
+        <v>124722787</v>
       </c>
       <c r="B68" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8675,38 +8656,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R68" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S68" t="n">
         <v>200</v>
@@ -8736,9 +8721,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8753,22 +8748,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124723379</v>
+        <v>124724006</v>
       </c>
       <c r="B69" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8777,20 +8772,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8801,17 +8796,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R69" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S69" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8850,7 +8845,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8870,17 +8865,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722787</v>
+        <v>124722855</v>
       </c>
       <c r="B70" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8889,30 +8884,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9223,6 +9223,366 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124847102</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57209</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>731492</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7537275</v>
+      </c>
+      <c r="S73" t="n">
+        <v>200</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>124847104</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58191</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>731492</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7537275</v>
+      </c>
+      <c r="S74" t="n">
+        <v>200</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>124847079</v>
+      </c>
+      <c r="B75" t="n">
+        <v>56610</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>102931</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bläsand</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Mareca penelope</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>731492</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7537275</v>
+      </c>
+      <c r="S75" t="n">
+        <v>200</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124712615</v>
+        <v>124724006</v>
       </c>
       <c r="B66" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,41 +8442,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731442</v>
+        <v>731578</v>
       </c>
       <c r="R66" t="n">
-        <v>7537393</v>
+        <v>7537099</v>
       </c>
       <c r="S66" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8503,9 +8503,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8520,22 +8530,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124723379</v>
+        <v>124712615</v>
       </c>
       <c r="B67" t="n">
-        <v>56563</v>
+        <v>56620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8544,25 +8554,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8572,10 +8582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R67" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S67" t="n">
         <v>200</v>
@@ -8605,19 +8615,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>20:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,12 +8632,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124724006</v>
+        <v>124723379</v>
       </c>
       <c r="B69" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8772,20 +8772,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8796,17 +8796,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R69" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S69" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B71" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,38 +9005,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9111,10 +9107,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B72" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9123,34 +9119,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847102</v>
+        <v>124847079</v>
       </c>
       <c r="B73" t="n">
-        <v>57209</v>
+        <v>56610</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100063</v>
+        <v>102931</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B75" t="n">
-        <v>56610</v>
+        <v>57209</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9582,6 +9582,454 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>124897287</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57157</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>731428</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7537475</v>
+      </c>
+      <c r="S76" t="n">
+        <v>200</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>124897267</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57143</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>731428</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7537475</v>
+      </c>
+      <c r="S77" t="n">
+        <v>200</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>124897293</v>
+      </c>
+      <c r="B78" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>731428</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7537475</v>
+      </c>
+      <c r="S78" t="n">
+        <v>200</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124897334</v>
+      </c>
+      <c r="B79" t="n">
+        <v>56610</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>102931</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bläsand</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Mareca penelope</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>731428</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7537475</v>
+      </c>
+      <c r="S79" t="n">
+        <v>200</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10031,6 +10031,126 @@
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>124930693</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57209</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>731407</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7537065</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B64" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,28 +8214,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8314,10 +8318,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B65" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8326,32 +8330,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124712615</v>
+        <v>124722855</v>
       </c>
       <c r="B67" t="n">
         <v>56620</v>
@@ -8575,17 +8575,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R67" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S67" t="n">
         <v>200</v>
@@ -8615,9 +8624,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,22 +8651,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124722787</v>
+        <v>124723379</v>
       </c>
       <c r="B68" t="n">
-        <v>56689</v>
+        <v>56563</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8660,16 +8679,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100079</v>
+        <v>100045</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8677,11 +8696,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8723,7 +8738,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8733,7 +8748,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8753,17 +8768,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124723379</v>
+        <v>124722787</v>
       </c>
       <c r="B69" t="n">
-        <v>56563</v>
+        <v>56689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8776,16 +8791,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100045</v>
+        <v>100079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8793,7 +8808,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8835,7 +8854,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8845,7 +8864,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8865,14 +8884,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722855</v>
+        <v>124712615</v>
       </c>
       <c r="B70" t="n">
         <v>56620</v>
@@ -8905,26 +8924,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R70" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S70" t="n">
         <v>200</v>
@@ -8954,19 +8964,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8981,12 +8981,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847104</v>
+        <v>124847102</v>
       </c>
       <c r="B74" t="n">
-        <v>58191</v>
+        <v>57209</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,30 +9357,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847102</v>
+        <v>124847104</v>
       </c>
       <c r="B75" t="n">
-        <v>57209</v>
+        <v>58191</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897267</v>
+        <v>124897293</v>
       </c>
       <c r="B77" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,20 +9709,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897293</v>
+        <v>124897267</v>
       </c>
       <c r="B78" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124724006</v>
+        <v>124723379</v>
       </c>
       <c r="B66" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,20 +8442,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8466,17 +8466,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R66" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S66" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8663,10 +8663,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124723379</v>
+        <v>124724006</v>
       </c>
       <c r="B68" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8675,20 +8675,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8699,17 +8699,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R68" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S68" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124722787</v>
+        <v>124712615</v>
       </c>
       <c r="B69" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8787,42 +8787,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R69" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S69" t="n">
         <v>200</v>
@@ -8852,19 +8848,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>20:51</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>20:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8879,22 +8865,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124712615</v>
+        <v>124722787</v>
       </c>
       <c r="B70" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8903,38 +8889,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R70" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S70" t="n">
         <v>200</v>
@@ -8964,9 +8954,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8981,22 +8981,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B71" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,34 +9005,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9107,10 +9111,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B72" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9119,38 +9123,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B73" t="n">
-        <v>56610</v>
+        <v>57209</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847102</v>
+        <v>124847079</v>
       </c>
       <c r="B74" t="n">
-        <v>57209</v>
+        <v>56610</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,30 +9357,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100063</v>
+        <v>102931</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897287</v>
+        <v>124897334</v>
       </c>
       <c r="B76" t="n">
-        <v>57157</v>
+        <v>56610</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9597,25 +9597,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102964</v>
+        <v>102931</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897293</v>
+        <v>124897287</v>
       </c>
       <c r="B77" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897334</v>
+        <v>124897293</v>
       </c>
       <c r="B79" t="n">
-        <v>56610</v>
+        <v>56563</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102931</v>
+        <v>100045</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B64" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,32 +8214,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8318,10 +8314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B65" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8330,28 +8326,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124723379</v>
+        <v>124722787</v>
       </c>
       <c r="B66" t="n">
-        <v>56563</v>
+        <v>56689</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8446,16 +8446,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100045</v>
+        <v>100079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8463,7 +8463,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8505,7 +8509,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8515,7 +8519,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8542,10 +8546,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124722855</v>
+        <v>124724006</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,50 +8558,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R67" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S67" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8626,7 +8621,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8636,7 +8631,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8663,10 +8658,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124724006</v>
+        <v>124722855</v>
       </c>
       <c r="B68" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8675,41 +8670,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R68" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S68" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8738,7 +8742,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8748,7 +8752,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8775,10 +8779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124712615</v>
+        <v>124723379</v>
       </c>
       <c r="B69" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8787,25 +8791,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8815,10 +8819,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R69" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S69" t="n">
         <v>200</v>
@@ -8848,9 +8852,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8865,22 +8879,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722787</v>
+        <v>124712615</v>
       </c>
       <c r="B70" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8889,42 +8903,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R70" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S70" t="n">
         <v>200</v>
@@ -8954,19 +8964,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:51</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8981,12 +8981,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847079</v>
+        <v>124847104</v>
       </c>
       <c r="B74" t="n">
-        <v>56610</v>
+        <v>58191</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,20 +9357,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102931</v>
+        <v>103044</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847104</v>
+        <v>124847079</v>
       </c>
       <c r="B75" t="n">
-        <v>58191</v>
+        <v>56610</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,20 +9477,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103044</v>
+        <v>102931</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897267</v>
+        <v>124897293</v>
       </c>
       <c r="B78" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897293</v>
+        <v>124897267</v>
       </c>
       <c r="B79" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124723379</v>
+        <v>124712615</v>
       </c>
       <c r="B69" t="n">
-        <v>56563</v>
+        <v>56620</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8791,25 +8791,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R69" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S69" t="n">
         <v>200</v>
@@ -8852,19 +8852,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>20:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8879,22 +8869,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124712615</v>
+        <v>124723379</v>
       </c>
       <c r="B70" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8903,25 +8893,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8931,10 +8921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R70" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S70" t="n">
         <v>200</v>
@@ -8964,9 +8954,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8981,12 +8981,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -10151,6 +10151,248 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125122872</v>
+      </c>
+      <c r="B81" t="n">
+        <v>56975</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>731578</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7537099</v>
+      </c>
+      <c r="S81" t="n">
+        <v>90</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125122775</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57209</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>731578</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7537099</v>
+      </c>
+      <c r="S82" t="n">
+        <v>90</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124722787</v>
+        <v>124723379</v>
       </c>
       <c r="B66" t="n">
-        <v>56689</v>
+        <v>56563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8446,16 +8446,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100079</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8463,11 +8463,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8509,7 +8505,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8519,7 +8515,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8539,17 +8535,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B67" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8558,41 +8554,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R67" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S67" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8619,19 +8615,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8646,22 +8632,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124722855</v>
+        <v>124724006</v>
       </c>
       <c r="B68" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8670,50 +8656,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R68" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S68" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8742,7 +8719,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8752,7 +8729,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8779,10 +8756,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124712615</v>
+        <v>124722787</v>
       </c>
       <c r="B69" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8791,38 +8768,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R69" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S69" t="n">
         <v>200</v>
@@ -8852,9 +8833,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8869,22 +8860,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124723379</v>
+        <v>124722855</v>
       </c>
       <c r="B70" t="n">
-        <v>56563</v>
+        <v>56620</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8893,28 +8884,37 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847102</v>
+        <v>124847104</v>
       </c>
       <c r="B73" t="n">
-        <v>57209</v>
+        <v>58191</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847104</v>
+        <v>124847079</v>
       </c>
       <c r="B74" t="n">
-        <v>58191</v>
+        <v>56610</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,20 +9357,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103044</v>
+        <v>102931</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B75" t="n">
-        <v>56610</v>
+        <v>57209</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897334</v>
+        <v>124897267</v>
       </c>
       <c r="B76" t="n">
-        <v>56610</v>
+        <v>57143</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9597,20 +9597,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102931</v>
+        <v>102963</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897267</v>
+        <v>124897334</v>
       </c>
       <c r="B79" t="n">
-        <v>57143</v>
+        <v>56610</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102963</v>
+        <v>102931</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B64" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,28 +8214,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8314,10 +8318,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B65" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8326,32 +8330,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124723379</v>
+        <v>124712615</v>
       </c>
       <c r="B66" t="n">
-        <v>56563</v>
+        <v>56620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,25 +8442,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R66" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S66" t="n">
         <v>200</v>
@@ -8503,19 +8503,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8530,22 +8520,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124712615</v>
+        <v>124724006</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,41 +8544,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731442</v>
+        <v>731578</v>
       </c>
       <c r="R67" t="n">
-        <v>7537393</v>
+        <v>7537099</v>
       </c>
       <c r="S67" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8615,9 +8605,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,22 +8632,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124724006</v>
+        <v>124722787</v>
       </c>
       <c r="B68" t="n">
-        <v>57143</v>
+        <v>56689</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8656,20 +8656,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102963</v>
+        <v>100079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8677,20 +8677,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R68" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S68" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8719,7 +8723,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8729,7 +8733,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8756,10 +8760,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124722787</v>
+        <v>124722855</v>
       </c>
       <c r="B69" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8768,30 +8772,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8835,7 +8844,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8845,7 +8854,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8872,10 +8881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722855</v>
+        <v>124723379</v>
       </c>
       <c r="B70" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8884,37 +8893,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B71" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,38 +9005,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9111,10 +9107,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B72" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9123,34 +9119,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847104</v>
+        <v>124847079</v>
       </c>
       <c r="B73" t="n">
-        <v>58191</v>
+        <v>56610</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,20 +9237,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>102931</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847079</v>
+        <v>124847104</v>
       </c>
       <c r="B74" t="n">
-        <v>56610</v>
+        <v>58191</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,20 +9357,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102931</v>
+        <v>103044</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897287</v>
+        <v>124897293</v>
       </c>
       <c r="B77" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897293</v>
+        <v>124897334</v>
       </c>
       <c r="B78" t="n">
-        <v>56563</v>
+        <v>56610</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100045</v>
+        <v>102931</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897334</v>
+        <v>124897287</v>
       </c>
       <c r="B79" t="n">
-        <v>56610</v>
+        <v>57157</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102931</v>
+        <v>102964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B81" t="n">
-        <v>56975</v>
+        <v>57209</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B82" t="n">
-        <v>57209</v>
+        <v>56975</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124712615</v>
+        <v>124724006</v>
       </c>
       <c r="B66" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,41 +8442,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731442</v>
+        <v>731578</v>
       </c>
       <c r="R66" t="n">
-        <v>7537393</v>
+        <v>7537099</v>
       </c>
       <c r="S66" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8503,9 +8503,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8520,22 +8530,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B67" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8544,41 +8554,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R67" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S67" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8605,19 +8615,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,12 +8632,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B71" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,34 +9005,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9107,10 +9111,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B72" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9119,38 +9123,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B66" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,41 +8442,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R66" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S66" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8503,19 +8503,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8530,22 +8520,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124712615</v>
+        <v>124724006</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,41 +8544,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731442</v>
+        <v>731578</v>
       </c>
       <c r="R67" t="n">
-        <v>7537393</v>
+        <v>7537099</v>
       </c>
       <c r="S67" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8615,9 +8605,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,12 +8632,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B71" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,38 +9005,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9111,10 +9107,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B72" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9123,34 +9119,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8532,10 +8532,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124724006</v>
+        <v>124722855</v>
       </c>
       <c r="B67" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8544,41 +8544,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R67" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S67" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8607,7 +8616,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8617,7 +8626,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8760,10 +8769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124722855</v>
+        <v>124724006</v>
       </c>
       <c r="B69" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8772,50 +8781,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R69" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S69" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8986,17 +8986,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B71" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,34 +9005,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9107,10 +9111,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B72" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9119,38 +9123,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897267</v>
+        <v>124897287</v>
       </c>
       <c r="B76" t="n">
-        <v>57143</v>
+        <v>57157</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9601,21 +9601,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102963</v>
+        <v>102964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897334</v>
+        <v>124897267</v>
       </c>
       <c r="B78" t="n">
-        <v>56610</v>
+        <v>57143</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102931</v>
+        <v>102963</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897287</v>
+        <v>124897334</v>
       </c>
       <c r="B79" t="n">
-        <v>57157</v>
+        <v>56610</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102964</v>
+        <v>102931</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B81" t="n">
-        <v>57209</v>
+        <v>56975</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B82" t="n">
-        <v>56975</v>
+        <v>57209</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124712615</v>
+        <v>124723379</v>
       </c>
       <c r="B66" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,25 +8442,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R66" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S66" t="n">
         <v>200</v>
@@ -8503,9 +8503,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8520,22 +8530,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124722855</v>
+        <v>124722787</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8544,35 +8554,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8616,7 +8621,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8626,7 +8631,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8653,10 +8658,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124722787</v>
+        <v>124722855</v>
       </c>
       <c r="B68" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8665,30 +8670,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8732,7 +8742,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8742,7 +8752,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8769,10 +8779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B69" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8781,41 +8791,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R69" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S69" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8842,19 +8852,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8869,22 +8869,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124723379</v>
+        <v>124724006</v>
       </c>
       <c r="B70" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8893,20 +8893,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8917,17 +8917,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R70" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S70" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897287</v>
+        <v>124897267</v>
       </c>
       <c r="B76" t="n">
-        <v>57157</v>
+        <v>57143</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9601,21 +9601,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897267</v>
+        <v>124897287</v>
       </c>
       <c r="B78" t="n">
-        <v>57143</v>
+        <v>57157</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9825,21 +9825,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102963</v>
+        <v>102964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B81" t="n">
-        <v>56975</v>
+        <v>57209</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B82" t="n">
-        <v>57209</v>
+        <v>56975</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8202,10 +8202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124617233</v>
+        <v>124617246</v>
       </c>
       <c r="B64" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8214,32 +8214,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8318,10 +8314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124617246</v>
+        <v>124617233</v>
       </c>
       <c r="B65" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8330,28 +8326,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124723379</v>
+        <v>124712615</v>
       </c>
       <c r="B66" t="n">
-        <v>56563</v>
+        <v>56620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,25 +8442,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R66" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S66" t="n">
         <v>200</v>
@@ -8503,19 +8503,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8530,22 +8520,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124722787</v>
+        <v>124724006</v>
       </c>
       <c r="B67" t="n">
-        <v>56689</v>
+        <v>57143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,20 +8544,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100079</v>
+        <v>102963</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8575,24 +8565,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R67" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S67" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8621,7 +8607,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8631,7 +8617,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8658,10 +8644,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124722855</v>
+        <v>124723379</v>
       </c>
       <c r="B68" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8670,37 +8656,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8742,7 +8719,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8752,7 +8729,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8772,17 +8749,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124712615</v>
+        <v>124722787</v>
       </c>
       <c r="B69" t="n">
-        <v>56620</v>
+        <v>56689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8791,38 +8768,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100006</v>
+        <v>100079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R69" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S69" t="n">
         <v>200</v>
@@ -8852,9 +8833,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8869,22 +8860,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124724006</v>
+        <v>124722855</v>
       </c>
       <c r="B70" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8893,41 +8884,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R70" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S70" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B73" t="n">
-        <v>56610</v>
+        <v>57209</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847102</v>
+        <v>124847079</v>
       </c>
       <c r="B75" t="n">
-        <v>57209</v>
+        <v>56610</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100063</v>
+        <v>102931</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897293</v>
+        <v>124897287</v>
       </c>
       <c r="B77" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897287</v>
+        <v>124897293</v>
       </c>
       <c r="B78" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,25 +9821,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124712615</v>
+        <v>124723379</v>
       </c>
       <c r="B66" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,25 +8442,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R66" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S66" t="n">
         <v>200</v>
@@ -8503,9 +8503,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8520,22 +8530,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B67" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8544,41 +8554,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R67" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S67" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8605,19 +8615,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8632,22 +8632,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124723379</v>
+        <v>124724006</v>
       </c>
       <c r="B68" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8656,20 +8656,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8680,17 +8680,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R68" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S68" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124723379</v>
+        <v>124722787</v>
       </c>
       <c r="B66" t="n">
-        <v>56563</v>
+        <v>56689</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8446,16 +8446,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100045</v>
+        <v>100079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8463,7 +8463,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8505,7 +8509,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8515,7 +8519,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8535,7 +8539,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8756,10 +8760,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124722787</v>
+        <v>124722855</v>
       </c>
       <c r="B69" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8768,30 +8772,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8835,7 +8844,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8845,7 +8854,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8872,10 +8881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722855</v>
+        <v>124723379</v>
       </c>
       <c r="B70" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8884,37 +8893,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897267</v>
+        <v>124897334</v>
       </c>
       <c r="B76" t="n">
-        <v>57143</v>
+        <v>56610</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9597,20 +9597,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102963</v>
+        <v>102931</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897287</v>
+        <v>124897293</v>
       </c>
       <c r="B77" t="n">
-        <v>57157</v>
+        <v>56563</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897293</v>
+        <v>124897287</v>
       </c>
       <c r="B78" t="n">
-        <v>56563</v>
+        <v>57157</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,25 +9821,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897334</v>
+        <v>124897267</v>
       </c>
       <c r="B79" t="n">
-        <v>56610</v>
+        <v>57143</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102931</v>
+        <v>102963</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B81" t="n">
-        <v>57209</v>
+        <v>56975</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B82" t="n">
-        <v>56975</v>
+        <v>57209</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124722787</v>
+        <v>124722855</v>
       </c>
       <c r="B66" t="n">
-        <v>56689</v>
+        <v>56620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,30 +8442,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100079</v>
+        <v>100006</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8509,7 +8514,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8519,7 +8524,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8539,17 +8544,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124712615</v>
+        <v>124723379</v>
       </c>
       <c r="B67" t="n">
-        <v>56620</v>
+        <v>56563</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8558,25 +8563,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8586,10 +8591,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R67" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S67" t="n">
         <v>200</v>
@@ -8619,9 +8624,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8636,22 +8651,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124724006</v>
+        <v>124712615</v>
       </c>
       <c r="B68" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8660,41 +8675,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731578</v>
+        <v>731442</v>
       </c>
       <c r="R68" t="n">
-        <v>7537099</v>
+        <v>7537393</v>
       </c>
       <c r="S68" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8721,19 +8736,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8748,22 +8753,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124722855</v>
+        <v>124724006</v>
       </c>
       <c r="B69" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8772,50 +8777,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R69" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S69" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8844,7 +8840,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8854,7 +8850,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8881,10 +8877,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124723379</v>
+        <v>124722787</v>
       </c>
       <c r="B70" t="n">
-        <v>56563</v>
+        <v>56689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8897,16 +8893,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100045</v>
+        <v>100079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8914,7 +8910,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B71" t="n">
-        <v>56620</v>
+        <v>57143</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,38 +9005,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9111,10 +9107,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B72" t="n">
-        <v>57143</v>
+        <v>56620</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9123,34 +9119,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847102</v>
+        <v>124847104</v>
       </c>
       <c r="B73" t="n">
-        <v>57209</v>
+        <v>58191</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847104</v>
+        <v>124847079</v>
       </c>
       <c r="B74" t="n">
-        <v>58191</v>
+        <v>56610</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,20 +9357,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103044</v>
+        <v>102931</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B75" t="n">
-        <v>56610</v>
+        <v>57209</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897334</v>
+        <v>124897287</v>
       </c>
       <c r="B76" t="n">
-        <v>56610</v>
+        <v>57157</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9597,25 +9597,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102931</v>
+        <v>102964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897293</v>
+        <v>124897267</v>
       </c>
       <c r="B77" t="n">
-        <v>56563</v>
+        <v>57143</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,20 +9709,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100045</v>
+        <v>102963</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897287</v>
+        <v>124897334</v>
       </c>
       <c r="B78" t="n">
-        <v>57157</v>
+        <v>56610</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,25 +9821,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102964</v>
+        <v>102931</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897267</v>
+        <v>124897293</v>
       </c>
       <c r="B79" t="n">
-        <v>57143</v>
+        <v>56563</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8205,7 +8205,7 @@
         <v>124617246</v>
       </c>
       <c r="B64" t="n">
-        <v>57157</v>
+        <v>57246</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>124617233</v>
       </c>
       <c r="B65" t="n">
-        <v>56563</v>
+        <v>56621</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124722855</v>
+        <v>124723379</v>
       </c>
       <c r="B66" t="n">
-        <v>56620</v>
+        <v>56621</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8442,37 +8442,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100006</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
@@ -8514,7 +8505,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8524,7 +8515,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8551,10 +8542,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124723379</v>
+        <v>124712615</v>
       </c>
       <c r="B67" t="n">
-        <v>56563</v>
+        <v>56795</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8563,25 +8554,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100045</v>
+        <v>100006</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8591,10 +8582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731461</v>
+        <v>731442</v>
       </c>
       <c r="R67" t="n">
-        <v>7537423</v>
+        <v>7537393</v>
       </c>
       <c r="S67" t="n">
         <v>200</v>
@@ -8624,19 +8615,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>20:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8651,22 +8632,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124712615</v>
+        <v>124722855</v>
       </c>
       <c r="B68" t="n">
-        <v>56620</v>
+        <v>56795</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8696,17 +8677,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731442</v>
+        <v>731461</v>
       </c>
       <c r="R68" t="n">
-        <v>7537393</v>
+        <v>7537423</v>
       </c>
       <c r="S68" t="n">
         <v>200</v>
@@ -8736,9 +8726,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8753,22 +8753,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124724006</v>
+        <v>124722787</v>
       </c>
       <c r="B69" t="n">
-        <v>57143</v>
+        <v>56740</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8777,20 +8777,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102963</v>
+        <v>100079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8798,20 +8798,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731578</v>
+        <v>731461</v>
       </c>
       <c r="R69" t="n">
-        <v>7537099</v>
+        <v>7537423</v>
       </c>
       <c r="S69" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8840,7 +8844,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8850,7 +8854,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8877,10 +8881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124722787</v>
+        <v>124724006</v>
       </c>
       <c r="B70" t="n">
-        <v>56689</v>
+        <v>57235</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8889,20 +8893,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100079</v>
+        <v>102963</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8910,24 +8914,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Luossalahti, Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731461</v>
+        <v>731578</v>
       </c>
       <c r="R70" t="n">
-        <v>7537423</v>
+        <v>7537099</v>
       </c>
       <c r="S70" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B71" t="n">
-        <v>57143</v>
+        <v>56795</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,34 +9005,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9107,10 +9111,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B72" t="n">
-        <v>56620</v>
+        <v>57235</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9119,38 +9123,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847104</v>
+        <v>124847102</v>
       </c>
       <c r="B73" t="n">
-        <v>58191</v>
+        <v>57290</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847079</v>
+        <v>124847104</v>
       </c>
       <c r="B74" t="n">
-        <v>56610</v>
+        <v>58305</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,20 +9357,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102931</v>
+        <v>103044</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847102</v>
+        <v>124847079</v>
       </c>
       <c r="B75" t="n">
-        <v>57209</v>
+        <v>56785</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,30 +9477,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100063</v>
+        <v>102931</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9588,7 +9588,7 @@
         <v>124897287</v>
       </c>
       <c r="B76" t="n">
-        <v>57157</v>
+        <v>57246</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897267</v>
+        <v>124897293</v>
       </c>
       <c r="B77" t="n">
-        <v>57143</v>
+        <v>56621</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,20 +9709,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897334</v>
+        <v>124897267</v>
       </c>
       <c r="B78" t="n">
-        <v>56610</v>
+        <v>57235</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102931</v>
+        <v>102963</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897293</v>
+        <v>124897334</v>
       </c>
       <c r="B79" t="n">
-        <v>56563</v>
+        <v>56785</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100045</v>
+        <v>102931</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10036,7 +10036,7 @@
         <v>124930693</v>
       </c>
       <c r="B80" t="n">
-        <v>57209</v>
+        <v>57290</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B81" t="n">
-        <v>56975</v>
+        <v>57290</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B82" t="n">
-        <v>57209</v>
+        <v>57059</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10392,6 +10392,138 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125551822</v>
+      </c>
+      <c r="B83" t="n">
+        <v>56740</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100079</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Salskrake</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mergellus albellus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sågviken, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>731492</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7537275</v>
+      </c>
+      <c r="S83" t="n">
+        <v>200</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -9225,10 +9225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124847102</v>
+        <v>124847104</v>
       </c>
       <c r="B73" t="n">
-        <v>57290</v>
+        <v>58305</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9237,30 +9237,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9345,10 +9345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847104</v>
+        <v>124847102</v>
       </c>
       <c r="B74" t="n">
-        <v>58305</v>
+        <v>57290</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9357,30 +9357,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9585,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897287</v>
+        <v>124897267</v>
       </c>
       <c r="B76" t="n">
-        <v>57246</v>
+        <v>57235</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9601,21 +9601,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897293</v>
+        <v>124897287</v>
       </c>
       <c r="B77" t="n">
-        <v>56621</v>
+        <v>57246</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124897267</v>
+        <v>124897334</v>
       </c>
       <c r="B78" t="n">
-        <v>57235</v>
+        <v>56785</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9821,20 +9821,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102963</v>
+        <v>102931</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897334</v>
+        <v>124897293</v>
       </c>
       <c r="B79" t="n">
-        <v>56785</v>
+        <v>56621</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9933,20 +9933,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102931</v>
+        <v>100045</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10153,10 +10153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125122775</v>
+        <v>125122872</v>
       </c>
       <c r="B81" t="n">
-        <v>57290</v>
+        <v>57059</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100063</v>
+        <v>102961</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,10 +10274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125122872</v>
+        <v>125122775</v>
       </c>
       <c r="B82" t="n">
-        <v>57059</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102961</v>
+        <v>100063</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124780623</v>
+        <v>124780549</v>
       </c>
       <c r="B71" t="n">
-        <v>56795</v>
+        <v>57235</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9005,38 +9005,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100006</v>
+        <v>102963</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -9111,10 +9107,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124780549</v>
+        <v>124780623</v>
       </c>
       <c r="B72" t="n">
-        <v>57235</v>
+        <v>56795</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9123,34 +9119,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102963</v>
+        <v>100006</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -10525,6 +10525,118 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125657134</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91860</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Luossalahti, Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>731120</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7537454</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -9230,11 +9230,6 @@
       <c r="B73" t="n">
         <v>58305</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>LC</t>
@@ -9345,42 +9340,37 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124847102</v>
+        <v>124847079</v>
       </c>
       <c r="B74" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56785</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100063</v>
+        <v>102931</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -9428,7 +9418,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9465,42 +9455,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124847079</v>
+        <v>124847102</v>
       </c>
       <c r="B75" t="n">
-        <v>56785</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57290</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102931</v>
+        <v>100063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -9548,7 +9533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9585,32 +9570,27 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124897267</v>
+        <v>124897293</v>
       </c>
       <c r="B76" t="n">
-        <v>57235</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56621</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102963</v>
+        <v>100045</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9697,15 +9677,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124897287</v>
+        <v>124897267</v>
       </c>
       <c r="B77" t="n">
-        <v>57246</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57235</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9713,21 +9688,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9814,11 +9789,6 @@
       <c r="B78" t="n">
         <v>56785</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>VU</t>
@@ -9921,37 +9891,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124897293</v>
+        <v>124897287</v>
       </c>
       <c r="B79" t="n">
-        <v>56621</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57246</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100045</v>
+        <v>102964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10038,11 +10003,6 @@
       <c r="B80" t="n">
         <v>57290</v>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>NT</t>
@@ -10156,12 +10116,7 @@
         <v>125122872</v>
       </c>
       <c r="B81" t="n">
-        <v>57059</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57069</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10277,12 +10232,7 @@
         <v>125122775</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57301</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10398,12 +10348,7 @@
         <v>125551822</v>
       </c>
       <c r="B83" t="n">
-        <v>56740</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56751</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10530,12 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91914</v>
+        <v>91921</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10577,6 +10577,244 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126026701</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57301</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Luossalahti, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>731396</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7537408</v>
+      </c>
+      <c r="S85" t="n">
+        <v>200</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Osborne Lindberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Osborne Lindberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126026749</v>
+      </c>
+      <c r="B86" t="n">
+        <v>56722</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>102108</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Alfågel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Clangula hyemalis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Luossalahti, Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>731396</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7537408</v>
+      </c>
+      <c r="S86" t="n">
+        <v>200</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Osborne Lindberg</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Osborne Lindberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91921</v>
+        <v>91925</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91925</v>
+        <v>91929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10815,6 +10815,585 @@
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126144059</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57069</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>730810</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7536965</v>
+      </c>
+      <c r="S87" t="n">
+        <v>50</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126144051</v>
+      </c>
+      <c r="B88" t="n">
+        <v>56795</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>102931</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Bläsand</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Mareca penelope</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>731458</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7537084</v>
+      </c>
+      <c r="S88" t="n">
+        <v>233</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126144060</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57257</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>731458</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7537084</v>
+      </c>
+      <c r="S89" t="n">
+        <v>233</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126144047</v>
+      </c>
+      <c r="B90" t="n">
+        <v>56751</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100079</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Salskrake</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Mergellus albellus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>731458</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7537084</v>
+      </c>
+      <c r="S90" t="n">
+        <v>233</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126144079</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Luossalahti, T lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>730810</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7536965</v>
+      </c>
+      <c r="S91" t="n">
+        <v>50</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marit Sikku Trägårdh</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11394,6 +11394,115 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>85384426</v>
+      </c>
+      <c r="B92" t="n">
+        <v>56667</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>232125</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skogsgås</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Anser fabalis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Latham, 1787)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sågviken Laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>731550</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7537353</v>
+      </c>
+      <c r="S92" t="n">
+        <v>50</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2020-05-12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2020-05-12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10348,7 +10348,7 @@
         <v>125551822</v>
       </c>
       <c r="B83" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91929</v>
+        <v>91931</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>126026701</v>
       </c>
       <c r="B85" t="n">
-        <v>57301</v>
+        <v>57302</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>126026749</v>
       </c>
       <c r="B86" t="n">
-        <v>56722</v>
+        <v>56723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10817,37 +10817,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126144059</v>
+        <v>126144051</v>
       </c>
       <c r="B87" t="n">
-        <v>57069</v>
+        <v>56796</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102961</v>
+        <v>102931</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10856,17 +10856,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R87" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10932,37 +10932,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126144051</v>
+        <v>126144059</v>
       </c>
       <c r="B88" t="n">
-        <v>56795</v>
+        <v>57070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102931</v>
+        <v>102961</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -10971,17 +10971,17 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R88" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S88" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11050,7 +11050,7 @@
         <v>126144060</v>
       </c>
       <c r="B89" t="n">
-        <v>57257</v>
+        <v>57258</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>126144047</v>
       </c>
       <c r="B90" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>126144079</v>
       </c>
       <c r="B91" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>85384426</v>
       </c>
       <c r="B92" t="n">
-        <v>56667</v>
+        <v>56668</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11166,32 +11166,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126144047</v>
+        <v>126144079</v>
       </c>
       <c r="B90" t="n">
-        <v>56752</v>
+        <v>58085</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100079</v>
+        <v>102999</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11205,17 +11205,17 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R90" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S90" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11281,32 +11281,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126144079</v>
+        <v>126144047</v>
       </c>
       <c r="B91" t="n">
-        <v>58085</v>
+        <v>56752</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102999</v>
+        <v>100079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11320,17 +11320,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R91" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91933</v>
+        <v>91935</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11166,32 +11166,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126144079</v>
+        <v>126144047</v>
       </c>
       <c r="B90" t="n">
-        <v>58085</v>
+        <v>56752</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102999</v>
+        <v>100079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11205,17 +11205,17 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R90" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11281,32 +11281,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126144047</v>
+        <v>126144079</v>
       </c>
       <c r="B91" t="n">
-        <v>56752</v>
+        <v>58085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100079</v>
+        <v>102999</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11320,17 +11320,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R91" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S91" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10475,7 +10475,7 @@
         <v>125657134</v>
       </c>
       <c r="B84" t="n">
-        <v>91935</v>
+        <v>91939</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>126026701</v>
       </c>
       <c r="B85" t="n">
-        <v>57302</v>
+        <v>57306</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>126026749</v>
       </c>
       <c r="B86" t="n">
-        <v>56723</v>
+        <v>56727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>126144051</v>
       </c>
       <c r="B87" t="n">
-        <v>56796</v>
+        <v>56800</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>126144059</v>
       </c>
       <c r="B88" t="n">
-        <v>57070</v>
+        <v>57074</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>126144060</v>
       </c>
       <c r="B89" t="n">
-        <v>57258</v>
+        <v>57262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>126144047</v>
       </c>
       <c r="B90" t="n">
-        <v>56752</v>
+        <v>56756</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>126144079</v>
       </c>
       <c r="B91" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>85384426</v>
       </c>
       <c r="B92" t="n">
-        <v>56668</v>
+        <v>56672</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10817,37 +10817,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126144051</v>
+        <v>126144059</v>
       </c>
       <c r="B87" t="n">
-        <v>56800</v>
+        <v>57074</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102931</v>
+        <v>102961</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10856,17 +10856,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R87" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S87" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10932,37 +10932,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126144059</v>
+        <v>126144051</v>
       </c>
       <c r="B88" t="n">
-        <v>57074</v>
+        <v>56800</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102961</v>
+        <v>102931</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -10971,17 +10971,17 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R88" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10582,7 +10582,7 @@
         <v>126026701</v>
       </c>
       <c r="B85" t="n">
-        <v>57306</v>
+        <v>57307</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>126026749</v>
       </c>
       <c r="B86" t="n">
-        <v>56727</v>
+        <v>56728</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>126144059</v>
       </c>
       <c r="B87" t="n">
-        <v>57074</v>
+        <v>57075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>126144051</v>
       </c>
       <c r="B88" t="n">
-        <v>56800</v>
+        <v>56801</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>126144060</v>
       </c>
       <c r="B89" t="n">
-        <v>57262</v>
+        <v>57263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11166,32 +11166,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126144047</v>
+        <v>126144079</v>
       </c>
       <c r="B90" t="n">
-        <v>56756</v>
+        <v>58092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100079</v>
+        <v>102999</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11205,17 +11205,17 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R90" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S90" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11281,32 +11281,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126144079</v>
+        <v>126144047</v>
       </c>
       <c r="B91" t="n">
-        <v>58089</v>
+        <v>56757</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102999</v>
+        <v>100079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11320,17 +11320,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R91" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11399,7 +11399,7 @@
         <v>85384426</v>
       </c>
       <c r="B92" t="n">
-        <v>56672</v>
+        <v>56673</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10817,37 +10817,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126144059</v>
+        <v>126144051</v>
       </c>
       <c r="B87" t="n">
-        <v>57075</v>
+        <v>56801</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102961</v>
+        <v>102931</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10856,17 +10856,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R87" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10932,37 +10932,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126144051</v>
+        <v>126144059</v>
       </c>
       <c r="B88" t="n">
-        <v>56801</v>
+        <v>57075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102931</v>
+        <v>102961</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -10971,17 +10971,17 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R88" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S88" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11166,32 +11166,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126144079</v>
+        <v>126144047</v>
       </c>
       <c r="B90" t="n">
-        <v>58092</v>
+        <v>56757</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102999</v>
+        <v>100079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11205,17 +11205,17 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R90" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11281,32 +11281,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126144047</v>
+        <v>126144079</v>
       </c>
       <c r="B91" t="n">
-        <v>56757</v>
+        <v>58092</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100079</v>
+        <v>102999</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11320,17 +11320,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R91" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S91" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -10817,37 +10817,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126144051</v>
+        <v>126144059</v>
       </c>
       <c r="B87" t="n">
-        <v>56801</v>
+        <v>57075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102931</v>
+        <v>102961</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10856,17 +10856,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lintasenniva, T lm</t>
+          <t>Luossalahti, T lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>731458</v>
+        <v>730810</v>
       </c>
       <c r="R87" t="n">
-        <v>7537084</v>
+        <v>7536965</v>
       </c>
       <c r="S87" t="n">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10932,37 +10932,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126144059</v>
+        <v>126144051</v>
       </c>
       <c r="B88" t="n">
-        <v>57075</v>
+        <v>56801</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102961</v>
+        <v>102931</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -10971,17 +10971,17 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Luossalahti, T lm</t>
+          <t>Lintasenniva, T lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730810</v>
+        <v>731458</v>
       </c>
       <c r="R88" t="n">
-        <v>7536965</v>
+        <v>7537084</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11503,6 +11503,122 @@
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127274044</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>laxforsen, laxforsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>731629</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7537090</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11508,7 +11508,7 @@
         <v>127274044</v>
       </c>
       <c r="B93" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11508,7 +11508,7 @@
         <v>127274044</v>
       </c>
       <c r="B93" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11508,7 +11508,7 @@
         <v>127274044</v>
       </c>
       <c r="B93" t="n">
-        <v>57676</v>
+        <v>57679</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11508,7 +11508,7 @@
         <v>127274044</v>
       </c>
       <c r="B93" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11619,6 +11619,117 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129227145</v>
+      </c>
+      <c r="B94" t="n">
+        <v>56697</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lintasenniva, Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>731569</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7537179</v>
+      </c>
+      <c r="S94" t="n">
+        <v>200</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11624,7 +11624,7 @@
         <v>129227145</v>
       </c>
       <c r="B94" t="n">
-        <v>56697</v>
+        <v>56699</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -11624,7 +11624,7 @@
         <v>129227145</v>
       </c>
       <c r="B94" t="n">
-        <v>56699</v>
+        <v>56701</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 55511-2020 artfynd.xlsx
+++ b/artfynd/A 55511-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11730,6 +11730,229 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129350996</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57337</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>731623</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7537168</v>
+      </c>
+      <c r="S95" t="n">
+        <v>52</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>mestadels adulter</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129350998</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57331</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lintasenniva, T lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>731623</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7537168</v>
+      </c>
+      <c r="S96" t="n">
+        <v>52</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Aron Andersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
